--- a/public/exports-with-coowners/11931316.xlsx
+++ b/public/exports-with-coowners/11931316.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/11931316.xlsx
+++ b/public/exports-with-coowners/11931316.xlsx
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 45</t>
+          <t xml:space="preserve">Vejlebrovej 57</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7856,11 +7856,11 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J105">
-        <v>11924</v>
+        <v>650</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7931,25 +7931,25 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>364</v>
+        <v>11924</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931691</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 47</t>
+          <t xml:space="preserve">Vejlebrovej 45</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8006,25 +8006,25 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J107">
-        <v>940</v>
+        <v>364</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931691</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vejlebrovej 57</t>
+          <t xml:space="preserve">Vejlebrovej 47</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J108">
-        <v>650</v>
+        <v>940</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873265</t>
+          <t xml:space="preserve">311931692</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-12</t>
+          <t xml:space="preserve">2036-10-14</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
